--- a/artfynd/A 50977-2021 artfynd.xlsx
+++ b/artfynd/A 50977-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129350374</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50977-2021 artfynd.xlsx
+++ b/artfynd/A 50977-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129350374</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50977-2021 artfynd.xlsx
+++ b/artfynd/A 50977-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129350374</v>
       </c>
       <c r="B2" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50977-2021 artfynd.xlsx
+++ b/artfynd/A 50977-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129350374</v>
+        <v>96325494</v>
       </c>
       <c r="B2" t="n">
-        <v>57894</v>
+        <v>89104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,49 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>805</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 50977, Lörstad, Sm</t>
+          <t>Lörstad, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572049</v>
+        <v>571987</v>
       </c>
       <c r="R2" t="n">
-        <v>6407092</v>
+        <v>6407165</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,21 +761,136 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129350374</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 50977, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572049</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6407092</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
